--- a/Excel_Practice/Data_Exploration/Order_Revenue_Data_Exploration/Order_Revenue_Dataset.xlsx
+++ b/Excel_Practice/Data_Exploration/Order_Revenue_Data_Exploration/Order_Revenue_Dataset.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mani_Entri_DA_Documents\Excel_Practice\Data_Exploration\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mani_Entri_DA_Documents\Excel_Practice\Data_Exploration\Order_Revenue_Data_Exploration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAADB2F8-0D2F-45C2-BCF5-8B44A96F6E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B2DA09-48FF-4803-8781-F0B9BCAE5500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{229DF1F8-FAC4-4D63-86DC-2F81015169E9}"/>
   </bookViews>
